--- a/tams-common-basicdata/src/main/resources/tpl/marketdata/valcoinfundquotationinfo/ValCoinFundQuotationInfo001.xlsx
+++ b/tams-common-basicdata/src/main/resources/tpl/marketdata/valcoinfundquotationinfo/ValCoinFundQuotationInfo001.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="2985"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14810" windowHeight="2990"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>基金代码</t>
   </si>
@@ -50,11 +50,18 @@
     <t>复权单位净值</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>基金总份额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -105,9 +112,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -126,7 +135,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -168,7 +177,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -203,7 +212,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -412,15 +421,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="18.5" customWidth="1"/>
-    <col min="8" max="8" width="8.75" customWidth="1"/>
-    <col min="9" max="9" width="12.375" customWidth="1"/>
+    <col min="7" max="7" width="18.453125" customWidth="1"/>
+    <col min="8" max="8" width="8.7265625" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.54296875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -448,7 +458,10 @@
       <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -462,7 +475,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -472,7 +485,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
